--- a/survey_templates/050_favorite_color_survey--survey_templates.xlsx
+++ b/survey_templates/050_favorite_color_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your favorite color</t>
+          <t>What is your favorite color?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>main_page_1</t>
+          <t>main_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,24 +554,24 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>main_page_2</t>
+          <t>main_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Select one or more</t>
+          <t>Do you like bright colors?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>main_page_3</t>
+          <t>main_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your favorite color</t>
+          <t>What is your favorite shade of your favorite color?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>main_page_4</t>
+          <t>main_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select one or more</t>
+          <t>Do you prefer warm or cool colors?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>main_page_5</t>
+          <t>main_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select one or more colors</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>main_page_6</t>
+          <t>main_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Select one or more</t>
+          <t>Do you like colors with high saturation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>main_page_7</t>
+          <t>main_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Select one or more</t>
+          <t>Select one or more colors from the palette</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>main_page_8</t>
+          <t>main_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your favorite color</t>
+          <t>Do you like colors with low saturation?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,338 +727,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>main_page_9</t>
+          <t>main_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select one or more</t>
+          <t>Select one or more colors from the range</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>main_page_10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Select one</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>main_page_11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>main_page_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>main_page_13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>main_page_14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>main_page_15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>main_page_16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>main_page_17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>main_page_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>main_page_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>main_page_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your favorite color</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>main_page_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>main_page_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>main_page_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select one or more</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,34 +781,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>main_page_1_choices</t>
+          <t>main_page_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>main_page_1_choices</t>
+          <t>main_page_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1142,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1159,29 +837,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>main_page_4_choices</t>
+          <t>main_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Purple</t>
         </is>
       </c>
     </row>
@@ -1193,29 +871,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>main_page_5_choices</t>
+          <t>main_page_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1227,29 +905,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>main_page_6_choices</t>
+          <t>main_page_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cool</t>
         </is>
       </c>
     </row>
@@ -1261,522 +939,199 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>main_page_7_choices</t>
+          <t>main_page_6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>main_page_7_choices</t>
+          <t>main_page_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>main_page_9_choices</t>
+          <t>main_page_6_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>main_page_9_choices</t>
+          <t>main_page_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pastel_pink</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pastel Pink</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>main_page_10_choices</t>
+          <t>main_page_8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>mint_green</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mint Green</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>main_page_10_choices</t>
+          <t>main_page_8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>royal_blue</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Royal Blue</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>main_page_11_choices</t>
+          <t>main_page_8_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sunshine_yellow</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sunshine Yellow</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>main_page_11_choices</t>
+          <t>main_page_10_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>main_page_12_choices</t>
+          <t>main_page_10_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>main_page_12_choices</t>
+          <t>main_page_10_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>red-violet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Red-Violet</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>main_page_13_choices</t>
+          <t>main_page_10_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yellow-green</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>main_page_13_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>main_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>main_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>main_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>main_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>main_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>main_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>main_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>main_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>main_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>main_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>main_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>main_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>main_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>main_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>main_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>main_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>main_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>main_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Yellow-Green</t>
         </is>
       </c>
     </row>
